--- a/InputData/elec/SoCtMbCtbDP/Shr of Costs that Must be Covered to be Deemed Profitable.xlsx
+++ b/InputData/elec/SoCtMbCtbDP/Shr of Costs that Must be Covered to be Deemed Profitable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us-analysis\InputData\elec\SoCtMbCtbDP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\SoCtMbCtbDP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C2FD9E-EFCC-4DF9-82F0-7BE08C7CAA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A19E10-E3AD-4C1E-90DB-DE9A677BADE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -506,14 +506,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DA106A-E484-4E2B-B3F9-91B326CF3E2A}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -521,22 +521,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -552,12 +552,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.5703125" customWidth="1"/>
+    <col min="1" max="1" width="34.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
@@ -565,7 +565,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -573,7 +573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -581,15 +581,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -597,103 +597,103 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>18</v>
       </c>
       <c r="B17">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -701,7 +701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -709,7 +709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -717,7 +717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -725,7 +725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -733,7 +733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -741,7 +741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -749,7 +749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>28</v>
       </c>

--- a/InputData/elec/SoCtMbCtbDP/Shr of Costs that Must be Covered to be Deemed Profitable.xlsx
+++ b/InputData/elec/SoCtMbCtbDP/Shr of Costs that Must be Covered to be Deemed Profitable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\SoCtMbCtbDP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A19E10-E3AD-4C1E-90DB-DE9A677BADE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3B09FC-ED01-4193-917B-AA2A38544B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>SoCtMbCtbDP Share of Costs that Must be Covered to be Deemed Profitable</t>
   </si>
@@ -124,18 +124,6 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
-  </si>
-  <si>
-    <t>We use higher values for power plant types that are early in their</t>
-  </si>
-  <si>
-    <t>learning curves (CCS and hydrogen power plants) and conventional</t>
-  </si>
-  <si>
-    <t>plant types that are not typically built on the basis of economics</t>
-  </si>
-  <si>
-    <t>today (coal, nuclear)</t>
   </si>
 </sst>
 </file>
@@ -505,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DA106A-E484-4E2B-B3F9-91B326CF3E2A}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -519,26 +507,6 @@
       </c>
       <c r="B3" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -586,7 +554,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -610,7 +578,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -618,7 +586,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -626,7 +594,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -634,7 +602,7 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -642,7 +610,7 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -650,7 +618,7 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -658,7 +626,7 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -666,7 +634,7 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -674,7 +642,7 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
